--- a/data/ICC.MI.xlsx
+++ b/data/ICC.MI.xlsx
@@ -27627,6 +27627,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1186">
+      <c r="A1186" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B1186" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1186" t="n">
+        <v>1.07000005245209</v>
+      </c>
+      <c r="D1186" t="n">
+        <v>1.07000005245209</v>
+      </c>
+      <c r="E1186" t="n">
+        <v>1.07000005245209</v>
+      </c>
+      <c r="F1186" t="n">
+        <v>1.07000005245209</v>
+      </c>
+      <c r="G1186" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ICC.MI.xlsx
+++ b/data/ICC.MI.xlsx
@@ -27650,6 +27650,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1187">
+      <c r="A1187" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B1187" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1187" t="n">
+        <v>1.07000005245209</v>
+      </c>
+      <c r="D1187" t="n">
+        <v>1.07000005245209</v>
+      </c>
+      <c r="E1187" t="n">
+        <v>1.07000005245209</v>
+      </c>
+      <c r="F1187" t="n">
+        <v>1.07000005245209</v>
+      </c>
+      <c r="G1187" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ICC.MI.xlsx
+++ b/data/ICC.MI.xlsx
@@ -27673,6 +27673,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1188">
+      <c r="A1188" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B1188" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1188" t="n">
+        <v>1.07000005245209</v>
+      </c>
+      <c r="D1188" t="n">
+        <v>1.07000005245209</v>
+      </c>
+      <c r="E1188" t="n">
+        <v>1.07000005245209</v>
+      </c>
+      <c r="F1188" t="n">
+        <v>1.07000005245209</v>
+      </c>
+      <c r="G1188" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ICC.MI.xlsx
+++ b/data/ICC.MI.xlsx
@@ -27537,22 +27537,22 @@
     </row>
     <row r="1182">
       <c r="A1182" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B1182" t="n">
-        <v>2250</v>
+        <v>0</v>
       </c>
       <c r="C1182" t="n">
-        <v>1.12999999523163</v>
+        <v>1.11000001430511</v>
       </c>
       <c r="D1182" t="n">
-        <v>1.12999999523163</v>
+        <v>1.11000001430511</v>
       </c>
       <c r="E1182" t="n">
-        <v>1.12999999523163</v>
+        <v>1.11000001430511</v>
       </c>
       <c r="F1182" t="n">
-        <v>1.12999999523163</v>
+        <v>1.11000001430511</v>
       </c>
       <c r="G1182" t="s">
         <v>7</v>
@@ -27560,22 +27560,22 @@
     </row>
     <row r="1183">
       <c r="A1183" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B1183" t="n">
-        <v>6000</v>
+        <v>2250</v>
       </c>
       <c r="C1183" t="n">
-        <v>1.11000001430511</v>
+        <v>1.12999999523163</v>
       </c>
       <c r="D1183" t="n">
-        <v>1.0900000333786</v>
+        <v>1.12999999523163</v>
       </c>
       <c r="E1183" t="n">
-        <v>1.11000001430511</v>
+        <v>1.12999999523163</v>
       </c>
       <c r="F1183" t="n">
-        <v>1.0900000333786</v>
+        <v>1.12999999523163</v>
       </c>
       <c r="G1183" t="s">
         <v>7</v>
@@ -27583,19 +27583,19 @@
     </row>
     <row r="1184">
       <c r="A1184" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B1184" t="n">
-        <v>0</v>
+        <v>6000</v>
       </c>
       <c r="C1184" t="n">
-        <v>1.0900000333786</v>
+        <v>1.11000001430511</v>
       </c>
       <c r="D1184" t="n">
         <v>1.0900000333786</v>
       </c>
       <c r="E1184" t="n">
-        <v>1.0900000333786</v>
+        <v>1.11000001430511</v>
       </c>
       <c r="F1184" t="n">
         <v>1.0900000333786</v>
@@ -27606,22 +27606,22 @@
     </row>
     <row r="1185">
       <c r="A1185" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B1185" t="n">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="C1185" t="n">
-        <v>1.07000005245209</v>
+        <v>1.0900000333786</v>
       </c>
       <c r="D1185" t="n">
-        <v>1.07000005245209</v>
+        <v>1.0900000333786</v>
       </c>
       <c r="E1185" t="n">
-        <v>1.07000005245209</v>
+        <v>1.0900000333786</v>
       </c>
       <c r="F1185" t="n">
-        <v>1.07000005245209</v>
+        <v>1.0900000333786</v>
       </c>
       <c r="G1185" t="s">
         <v>7</v>
@@ -27629,10 +27629,10 @@
     </row>
     <row r="1186">
       <c r="A1186" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B1186" t="n">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="C1186" t="n">
         <v>1.07000005245209</v>
@@ -27652,7 +27652,7 @@
     </row>
     <row r="1187">
       <c r="A1187" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B1187" t="n">
         <v>0</v>
@@ -27675,7 +27675,7 @@
     </row>
     <row r="1188">
       <c r="A1188" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B1188" t="n">
         <v>0</v>
@@ -27693,6 +27693,29 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G1188" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1189">
+      <c r="A1189" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B1189" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1189" t="n">
+        <v>1.07000005245209</v>
+      </c>
+      <c r="D1189" t="n">
+        <v>1.07000005245209</v>
+      </c>
+      <c r="E1189" t="n">
+        <v>1.07000005245209</v>
+      </c>
+      <c r="F1189" t="n">
+        <v>1.07000005245209</v>
+      </c>
+      <c r="G1189" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/ICC.MI.xlsx
+++ b/data/ICC.MI.xlsx
@@ -27719,6 +27719,52 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1190">
+      <c r="A1190" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B1190" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1190" t="n">
+        <v>1.07000005245209</v>
+      </c>
+      <c r="D1190" t="n">
+        <v>1.07000005245209</v>
+      </c>
+      <c r="E1190" t="n">
+        <v>1.07000005245209</v>
+      </c>
+      <c r="F1190" t="n">
+        <v>1.07000005245209</v>
+      </c>
+      <c r="G1190" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1191">
+      <c r="A1191" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B1191" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1191" t="n">
+        <v>1.07000005245209</v>
+      </c>
+      <c r="D1191" t="n">
+        <v>1.07000005245209</v>
+      </c>
+      <c r="E1191" t="n">
+        <v>1.07000005245209</v>
+      </c>
+      <c r="F1191" t="n">
+        <v>1.07000005245209</v>
+      </c>
+      <c r="G1191" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ICC.MI.xlsx
+++ b/data/ICC.MI.xlsx
@@ -27765,6 +27765,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1192">
+      <c r="A1192" s="1" t="n">
+        <v>46286.2916666667</v>
+      </c>
+      <c r="B1192" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1192" t="n">
+        <v>1.07000005245209</v>
+      </c>
+      <c r="D1192" t="n">
+        <v>1.07000005245209</v>
+      </c>
+      <c r="E1192" t="n">
+        <v>1.07000005245209</v>
+      </c>
+      <c r="F1192" t="n">
+        <v>1.07000005245209</v>
+      </c>
+      <c r="G1192" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ICC.MI.xlsx
+++ b/data/ICC.MI.xlsx
@@ -27788,6 +27788,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1193">
+      <c r="A1193" s="1" t="n">
+        <v>46287.2916666667</v>
+      </c>
+      <c r="B1193" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1193" t="n">
+        <v>1.07000005245209</v>
+      </c>
+      <c r="D1193" t="n">
+        <v>1.07000005245209</v>
+      </c>
+      <c r="E1193" t="n">
+        <v>1.07000005245209</v>
+      </c>
+      <c r="F1193" t="n">
+        <v>1.07000005245209</v>
+      </c>
+      <c r="G1193" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ICC.MI.xlsx
+++ b/data/ICC.MI.xlsx
@@ -27811,6 +27811,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1194">
+      <c r="A1194" s="1" t="n">
+        <v>46288.2916666667</v>
+      </c>
+      <c r="B1194" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1194" t="n">
+        <v>1.07000005245209</v>
+      </c>
+      <c r="D1194" t="n">
+        <v>1.07000005245209</v>
+      </c>
+      <c r="E1194" t="n">
+        <v>1.07000005245209</v>
+      </c>
+      <c r="F1194" t="n">
+        <v>1.07000005245209</v>
+      </c>
+      <c r="G1194" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ICC.MI.xlsx
+++ b/data/ICC.MI.xlsx
@@ -27834,6 +27834,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1195">
+      <c r="A1195" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B1195" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1195" t="n">
+        <v>1.07000005245209</v>
+      </c>
+      <c r="D1195" t="n">
+        <v>1.07000005245209</v>
+      </c>
+      <c r="E1195" t="n">
+        <v>1.07000005245209</v>
+      </c>
+      <c r="F1195" t="n">
+        <v>1.07000005245209</v>
+      </c>
+      <c r="G1195" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ICC.MI.xlsx
+++ b/data/ICC.MI.xlsx
@@ -27857,6 +27857,50 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1196">
+      <c r="A1196" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B1196" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1196" t="n">
+        <v>1.07000005245209</v>
+      </c>
+      <c r="D1196" t="n">
+        <v>1.07000005245209</v>
+      </c>
+      <c r="E1196" t="n">
+        <v>1.07000005245209</v>
+      </c>
+      <c r="F1196" t="n">
+        <v>1.07000005245209</v>
+      </c>
+      <c r="G1196" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1197">
+      <c r="A1197" s="1" t="n">
+        <v>46293.2916666667</v>
+      </c>
+      <c r="B1197" t="n">
+        <v>3750</v>
+      </c>
+      <c r="C1197" t="n">
+        <v>1.0900000333786</v>
+      </c>
+      <c r="D1197" t="n">
+        <v>1.07000005245209</v>
+      </c>
+      <c r="E1197" t="n">
+        <v>1.0900000333786</v>
+      </c>
+      <c r="F1197"/>
+      <c r="G1197" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ICC.MI.xlsx
+++ b/data/ICC.MI.xlsx
@@ -27896,7 +27896,9 @@
       <c r="E1197" t="n">
         <v>1.0900000333786</v>
       </c>
-      <c r="F1197"/>
+      <c r="F1197" t="n">
+        <v>1.07000005245209</v>
+      </c>
       <c r="G1197" t="s">
         <v>7</v>
       </c>

--- a/data/ICC.MI.xlsx
+++ b/data/ICC.MI.xlsx
@@ -27903,6 +27903,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1198">
+      <c r="A1198" s="1" t="n">
+        <v>46294.2916666667</v>
+      </c>
+      <c r="B1198" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1198" t="n">
+        <v>1.07000005245209</v>
+      </c>
+      <c r="D1198" t="n">
+        <v>1.07000005245209</v>
+      </c>
+      <c r="E1198" t="n">
+        <v>1.07000005245209</v>
+      </c>
+      <c r="F1198" t="n">
+        <v>1.07000005245209</v>
+      </c>
+      <c r="G1198" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ICC.MI.xlsx
+++ b/data/ICC.MI.xlsx
@@ -27926,6 +27926,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1199">
+      <c r="A1199" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B1199" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1199" t="n">
+        <v>1.07000005245209</v>
+      </c>
+      <c r="D1199" t="n">
+        <v>1.07000005245209</v>
+      </c>
+      <c r="E1199" t="n">
+        <v>1.07000005245209</v>
+      </c>
+      <c r="F1199" t="n">
+        <v>1.07000005245209</v>
+      </c>
+      <c r="G1199" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ICC.MI.xlsx
+++ b/data/ICC.MI.xlsx
@@ -27949,6 +27949,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1200">
+      <c r="A1200" s="1" t="n">
+        <v>46296.2916666667</v>
+      </c>
+      <c r="B1200" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1200" t="n">
+        <v>1.07000005245209</v>
+      </c>
+      <c r="D1200" t="n">
+        <v>1.07000005245209</v>
+      </c>
+      <c r="E1200" t="n">
+        <v>1.07000005245209</v>
+      </c>
+      <c r="F1200" t="n">
+        <v>1.07000005245209</v>
+      </c>
+      <c r="G1200" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ICC.MI.xlsx
+++ b/data/ICC.MI.xlsx
@@ -27972,6 +27972,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1201">
+      <c r="A1201" s="1" t="n">
+        <v>46297.2916666667</v>
+      </c>
+      <c r="B1201" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1201" t="n">
+        <v>1.07000005245209</v>
+      </c>
+      <c r="D1201" t="n">
+        <v>1.07000005245209</v>
+      </c>
+      <c r="E1201" t="n">
+        <v>1.07000005245209</v>
+      </c>
+      <c r="F1201" t="n">
+        <v>1.07000005245209</v>
+      </c>
+      <c r="G1201" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ICC.MI.xlsx
+++ b/data/ICC.MI.xlsx
@@ -27995,6 +27995,50 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1202">
+      <c r="A1202" s="1" t="n">
+        <v>46300.2916666667</v>
+      </c>
+      <c r="B1202" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1202" t="n">
+        <v>1.07000005245209</v>
+      </c>
+      <c r="D1202" t="n">
+        <v>1.07000005245209</v>
+      </c>
+      <c r="E1202" t="n">
+        <v>1.07000005245209</v>
+      </c>
+      <c r="F1202" t="n">
+        <v>1.07000005245209</v>
+      </c>
+      <c r="G1202" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1203">
+      <c r="A1203" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B1203" t="n">
+        <v>2250</v>
+      </c>
+      <c r="C1203" t="n">
+        <v>1.07000005245209</v>
+      </c>
+      <c r="D1203" t="n">
+        <v>1.04999995231628</v>
+      </c>
+      <c r="E1203" t="n">
+        <v>1.04999995231628</v>
+      </c>
+      <c r="F1203"/>
+      <c r="G1203" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ICC.MI.xlsx
+++ b/data/ICC.MI.xlsx
@@ -28034,8 +28034,31 @@
       <c r="E1203" t="n">
         <v>1.04999995231628</v>
       </c>
-      <c r="F1203"/>
+      <c r="F1203" t="n">
+        <v>1.07000005245209</v>
+      </c>
       <c r="G1203" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1204">
+      <c r="A1204" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B1204" t="n">
+        <v>6750</v>
+      </c>
+      <c r="C1204" t="n">
+        <v>1.03999996185303</v>
+      </c>
+      <c r="D1204" t="n">
+        <v>1.00999999046326</v>
+      </c>
+      <c r="E1204" t="n">
+        <v>1.03999996185303</v>
+      </c>
+      <c r="F1204"/>
+      <c r="G1204" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/ICC.MI.xlsx
+++ b/data/ICC.MI.xlsx
@@ -28057,8 +28057,31 @@
       <c r="E1204" t="n">
         <v>1.03999996185303</v>
       </c>
-      <c r="F1204"/>
+      <c r="F1204" t="n">
+        <v>1.00999999046326</v>
+      </c>
       <c r="G1204" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1205">
+      <c r="A1205" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B1205" t="n">
+        <v>750</v>
+      </c>
+      <c r="C1205" t="n">
+        <v>1.00999999046326</v>
+      </c>
+      <c r="D1205" t="n">
+        <v>1.00999999046326</v>
+      </c>
+      <c r="E1205" t="n">
+        <v>1.00999999046326</v>
+      </c>
+      <c r="F1205"/>
+      <c r="G1205" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/ICC.MI.xlsx
+++ b/data/ICC.MI.xlsx
@@ -28080,8 +28080,31 @@
       <c r="E1205" t="n">
         <v>1.00999999046326</v>
       </c>
-      <c r="F1205"/>
+      <c r="F1205" t="n">
+        <v>1.00999999046326</v>
+      </c>
       <c r="G1205" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1206">
+      <c r="A1206" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B1206" t="n">
+        <v>750</v>
+      </c>
+      <c r="C1206" t="n">
+        <v>0.985000014305115</v>
+      </c>
+      <c r="D1206" t="n">
+        <v>0.985000014305115</v>
+      </c>
+      <c r="E1206" t="n">
+        <v>0.985000014305115</v>
+      </c>
+      <c r="F1206"/>
+      <c r="G1206" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/ICC.MI.xlsx
+++ b/data/ICC.MI.xlsx
@@ -28110,6 +28110,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1207">
+      <c r="A1207" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B1207" t="n">
+        <v>19500</v>
+      </c>
+      <c r="C1207" t="n">
+        <v>1.10000002384186</v>
+      </c>
+      <c r="D1207" t="n">
+        <v>0.990000009536743</v>
+      </c>
+      <c r="E1207" t="n">
+        <v>0.990000009536743</v>
+      </c>
+      <c r="F1207" t="n">
+        <v>1.10000002384186</v>
+      </c>
+      <c r="G1207" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ICC.MI.xlsx
+++ b/data/ICC.MI.xlsx
@@ -28179,6 +28179,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1210">
+      <c r="A1210" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B1210" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1210" t="n">
+        <v>1.10000002384186</v>
+      </c>
+      <c r="D1210" t="n">
+        <v>1.10000002384186</v>
+      </c>
+      <c r="E1210" t="n">
+        <v>1.10000002384186</v>
+      </c>
+      <c r="F1210" t="n">
+        <v>1.10000002384186</v>
+      </c>
+      <c r="G1210" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ICC.MI.xlsx
+++ b/data/ICC.MI.xlsx
@@ -35497,6 +35497,64 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1212">
+      <c r="A1212" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1212" s="1" t="n">
+        <v>46314.2916666667</v>
+      </c>
+      <c r="C1212" t="n">
+        <v>1.07000005245209</v>
+      </c>
+      <c r="D1212" t="n">
+        <v>1.07000005245209</v>
+      </c>
+      <c r="E1212" t="n">
+        <v>1.07000005245209</v>
+      </c>
+      <c r="F1212" t="n">
+        <v>1.07000005245209</v>
+      </c>
+      <c r="G1212" t="n">
+        <v>1.07000005245209</v>
+      </c>
+      <c r="H1212" t="n">
+        <v>3000</v>
+      </c>
+      <c r="I1212" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1213">
+      <c r="A1213" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1213" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C1213" t="n">
+        <v>1.03999996185303</v>
+      </c>
+      <c r="D1213" t="n">
+        <v>1.05999994277954</v>
+      </c>
+      <c r="E1213" t="n">
+        <v>1.03999996185303</v>
+      </c>
+      <c r="F1213" t="n">
+        <v>1.05999994277954</v>
+      </c>
+      <c r="G1213" t="n">
+        <v>1.05999994277954</v>
+      </c>
+      <c r="H1213" t="n">
+        <v>16500</v>
+      </c>
+      <c r="I1213" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ICC.MI.xlsx
+++ b/data/ICC.MI.xlsx
@@ -35555,6 +35555,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1214">
+      <c r="A1214" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1214" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C1214" t="n">
+        <v>1.03999996185303</v>
+      </c>
+      <c r="D1214" t="n">
+        <v>1.04999995231628</v>
+      </c>
+      <c r="E1214" t="n">
+        <v>1.00999999046326</v>
+      </c>
+      <c r="F1214" t="n">
+        <v>1.04999995231628</v>
+      </c>
+      <c r="G1214" t="n">
+        <v>1.04999995231628</v>
+      </c>
+      <c r="H1214" t="n">
+        <v>7500</v>
+      </c>
+      <c r="I1214" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ICC.MI.xlsx
+++ b/data/ICC.MI.xlsx
@@ -35584,6 +35584,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1215">
+      <c r="A1215" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1215" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C1215" t="n">
+        <v>1.04999995231628</v>
+      </c>
+      <c r="D1215" t="n">
+        <v>1.04999995231628</v>
+      </c>
+      <c r="E1215" t="n">
+        <v>1.04999995231628</v>
+      </c>
+      <c r="F1215" t="n">
+        <v>1.04999995231628</v>
+      </c>
+      <c r="G1215" t="n">
+        <v>1.04999995231628</v>
+      </c>
+      <c r="H1215" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1215" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ICC.MI.xlsx
+++ b/data/ICC.MI.xlsx
@@ -35613,6 +35613,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1216">
+      <c r="A1216" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1216" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C1216" t="n">
+        <v>1.04999995231628</v>
+      </c>
+      <c r="D1216" t="n">
+        <v>1.04999995231628</v>
+      </c>
+      <c r="E1216" t="n">
+        <v>1.04999995231628</v>
+      </c>
+      <c r="F1216" t="n">
+        <v>1.04999995231628</v>
+      </c>
+      <c r="G1216" t="n">
+        <v>1.04999995231628</v>
+      </c>
+      <c r="H1216" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1216" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ICC.MI.xlsx
+++ b/data/ICC.MI.xlsx
@@ -35642,6 +35642,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1217">
+      <c r="A1217" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1217" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C1217" t="n">
+        <v>1.04999995231628</v>
+      </c>
+      <c r="D1217" t="n">
+        <v>1.04999995231628</v>
+      </c>
+      <c r="E1217" t="n">
+        <v>1.04999995231628</v>
+      </c>
+      <c r="F1217" t="n">
+        <v>1.04999995231628</v>
+      </c>
+      <c r="G1217" t="n">
+        <v>1.04999995231628</v>
+      </c>
+      <c r="H1217" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1217" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ICC.MI.xlsx
+++ b/data/ICC.MI.xlsx
@@ -35671,6 +35671,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1218">
+      <c r="A1218" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1218" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C1218" t="n">
+        <v>1.04999995231628</v>
+      </c>
+      <c r="D1218" t="n">
+        <v>1.04999995231628</v>
+      </c>
+      <c r="E1218" t="n">
+        <v>1.04999995231628</v>
+      </c>
+      <c r="F1218" t="n">
+        <v>1.04999995231628</v>
+      </c>
+      <c r="G1218" t="n">
+        <v>1.04999995231628</v>
+      </c>
+      <c r="H1218" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1218" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ICC.MI.xlsx
+++ b/data/ICC.MI.xlsx
@@ -35700,6 +35700,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1219">
+      <c r="A1219" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1219" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C1219" t="n">
+        <v>1.04999995231628</v>
+      </c>
+      <c r="D1219" t="n">
+        <v>1.04999995231628</v>
+      </c>
+      <c r="E1219" t="n">
+        <v>1.04999995231628</v>
+      </c>
+      <c r="F1219" t="n">
+        <v>1.04999995231628</v>
+      </c>
+      <c r="G1219" t="n">
+        <v>1.04999995231628</v>
+      </c>
+      <c r="H1219" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1219" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ICC.MI.xlsx
+++ b/data/ICC.MI.xlsx
@@ -35729,6 +35729,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1220">
+      <c r="A1220" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1220" s="1" t="n">
+        <v>46324.3333333333</v>
+      </c>
+      <c r="C1220" t="n">
+        <v>1.04999995231628</v>
+      </c>
+      <c r="D1220" t="n">
+        <v>1.04999995231628</v>
+      </c>
+      <c r="E1220" t="n">
+        <v>1.04999995231628</v>
+      </c>
+      <c r="F1220" t="n">
+        <v>1.04999995231628</v>
+      </c>
+      <c r="G1220" t="n">
+        <v>1.04999995231628</v>
+      </c>
+      <c r="H1220" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1220" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
